--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7938,0.0895,0.0817,0.0569</t>
-  </si>
-  <si>
-    <t>0.0789,0.0195,0.0078,0.9580</t>
-  </si>
-  <si>
-    <t>0.7700,0.1061,0.0500,0.1442</t>
-  </si>
-  <si>
-    <t>0.1036,0.0360,0.0020,0.9538</t>
-  </si>
-  <si>
-    <t>0.9908,0.0046,0.0006,0.0027</t>
-  </si>
-  <si>
-    <t>0.9844,0.0084,0.0011,0.0043</t>
-  </si>
-  <si>
-    <t>0.9833,0.0060,0.0017,0.0060</t>
-  </si>
-  <si>
-    <t>0.9774,0.0086,0.0024,0.0081</t>
-  </si>
-  <si>
-    <t>0.9885,0.0053,0.0007,0.0037</t>
-  </si>
-  <si>
-    <t>0.9793,0.0141,0.0016,0.0035</t>
-  </si>
-  <si>
-    <t>0.9881,0.0054,0.0007,0.0044</t>
-  </si>
-  <si>
-    <t>0.9892,0.0065,0.0008,0.0026</t>
-  </si>
-  <si>
-    <t>0.3150,0.4382,0.2919,0.0419</t>
-  </si>
-  <si>
-    <t>0.2628,0.1507,0.6551,0.0180</t>
-  </si>
-  <si>
-    <t>0.1342,0.1337,0.7910,0.0115</t>
-  </si>
-  <si>
-    <t>0.0631,0.5538,0.5542,0.0081</t>
-  </si>
-  <si>
-    <t>0.3857,0.2170,0.4168,0.0275</t>
-  </si>
-  <si>
-    <t>0.1066,0.8417,0.0725,0.0043</t>
-  </si>
-  <si>
-    <t>0.1720,0.8035,0.0534,0.0055</t>
-  </si>
-  <si>
-    <t>0.4711,0.5843,0.0319,0.0094</t>
-  </si>
-  <si>
-    <t>0.3634,0.6878,0.0257,0.0112</t>
-  </si>
-  <si>
-    <t>0.0569,0.9343,0.0268,0.0016</t>
-  </si>
-  <si>
-    <t>0.2124,0.0465,0.7541,0.0592</t>
-  </si>
-  <si>
-    <t>0.1478,0.1031,0.6932,0.1410</t>
-  </si>
-  <si>
-    <t>0.0458,0.0372,0.9282,0.0224</t>
-  </si>
-  <si>
-    <t>0.2271,0.0376,0.7317,0.0826</t>
-  </si>
-  <si>
-    <t>0.1639,0.0767,0.7918,0.0448</t>
-  </si>
-  <si>
-    <t>0.1282,0.0447,0.8503,0.0366</t>
-  </si>
-  <si>
-    <t>0.0516,0.0548,0.9121,0.0236</t>
-  </si>
-  <si>
-    <t>0.3387,0.6727,0.0594,0.0170</t>
-  </si>
-  <si>
-    <t>0.3921,0.3446,0.3015,0.0259</t>
-  </si>
-  <si>
-    <t>0.1118,0.2511,0.7611,0.0563</t>
-  </si>
-  <si>
-    <t>0.0343,0.8896,0.1492,0.0026</t>
-  </si>
-  <si>
-    <t>0.7424,0.2224,0.0540,0.0161</t>
-  </si>
-  <si>
-    <t>0.8750,0.0821,0.0353,0.0227</t>
-  </si>
-  <si>
-    <t>0.7984,0.2243,0.0243,0.0058</t>
-  </si>
-  <si>
-    <t>0.0739,0.8691,0.0976,0.0092</t>
-  </si>
-  <si>
-    <t>0.0356,0.8159,0.4049,0.0401</t>
-  </si>
-  <si>
-    <t>0.0168,0.0358,0.9421,0.0450</t>
-  </si>
-  <si>
-    <t>0.0288,0.5664,0.7072,0.0247</t>
-  </si>
-  <si>
-    <t>0.0360,0.0226,0.9182,0.0543</t>
-  </si>
-  <si>
-    <t>0.0451,0.6390,0.6375,0.0139</t>
-  </si>
-  <si>
-    <t>0.0162,0.9163,0.2467,0.0045</t>
-  </si>
-  <si>
-    <t>0.0213,0.3178,0.9108,0.0055</t>
-  </si>
-  <si>
-    <t>0.1767,0.3403,0.0235,0.8229</t>
-  </si>
-  <si>
-    <t>0.0199,0.9551,0.0280,0.0127</t>
-  </si>
-  <si>
-    <t>0.0198,0.9483,0.0855,0.0046</t>
-  </si>
-  <si>
-    <t>0.0055,0.9858,0.0191,0.0018</t>
-  </si>
-  <si>
-    <t>0.0523,0.5200,0.6251,0.0556</t>
-  </si>
-  <si>
-    <t>0.0180,0.1627,0.9396,0.0102</t>
-  </si>
-  <si>
-    <t>0.0965,0.0982,0.8481,0.0392</t>
-  </si>
-  <si>
-    <t>0.2212,0.0532,0.7119,0.0826</t>
-  </si>
-  <si>
-    <t>0.0051,0.0721,0.9847,0.0035</t>
-  </si>
-  <si>
-    <t>0.0133,0.1068,0.9641,0.0025</t>
-  </si>
-  <si>
-    <t>0.9805,0.0108,0.0018,0.0049</t>
-  </si>
-  <si>
-    <t>0.9814,0.0105,0.0015,0.0045</t>
-  </si>
-  <si>
-    <t>0.9684,0.0241,0.0033,0.0056</t>
-  </si>
-  <si>
-    <t>0.1740,0.1224,0.7748,0.0445</t>
-  </si>
-  <si>
-    <t>0.9818,0.0121,0.0015,0.0039</t>
-  </si>
-  <si>
-    <t>0.9890,0.0077,0.0006,0.0023</t>
-  </si>
-  <si>
-    <t>0.9544,0.0407,0.0064,0.0054</t>
-  </si>
-  <si>
-    <t>0.0035,0.9554,0.4856,0.0015</t>
-  </si>
-  <si>
-    <t>0.0135,0.4020,0.9120,0.0051</t>
-  </si>
-  <si>
-    <t>0.0094,0.1508,0.9582,0.0078</t>
-  </si>
-  <si>
-    <t>0.0060,0.4152,0.9596,0.0023</t>
-  </si>
-  <si>
-    <t>0.0133,0.0446,0.9700,0.0095</t>
-  </si>
-  <si>
-    <t>0.0536,0.8852,0.1154,0.0046</t>
-  </si>
-  <si>
-    <t>0.0061,0.9879,0.0082,0.0007</t>
-  </si>
-  <si>
-    <t>0.7810,0.1082,0.1176,0.0262</t>
-  </si>
-  <si>
-    <t>0.5055,0.4448,0.0988,0.0197</t>
-  </si>
-  <si>
-    <t>0.2244,0.2970,0.5903,0.0188</t>
-  </si>
-  <si>
-    <t>0.0150,0.6668,0.8207,0.0066</t>
-  </si>
-  <si>
-    <t>0.0107,0.8675,0.6174,0.0060</t>
-  </si>
-  <si>
-    <t>0.0131,0.9078,0.3947,0.0060</t>
-  </si>
-  <si>
-    <t>0.0127,0.6911,0.8109,0.0053</t>
-  </si>
-  <si>
-    <t>0.3532,0.0380,0.1783,0.5216</t>
-  </si>
-  <si>
-    <t>0.0537,0.0337,0.0021,0.9758</t>
-  </si>
-  <si>
-    <t>0.0085,0.0180,0.0028,0.9929</t>
-  </si>
-  <si>
-    <t>0.0757,0.0919,0.0110,0.9518</t>
-  </si>
-  <si>
-    <t>0.0574,0.0234,0.0057,0.9690</t>
-  </si>
-  <si>
-    <t>0.0222,0.0449,0.0054,0.9831</t>
-  </si>
-  <si>
-    <t>0.0109,0.8666,0.6799,0.0058</t>
-  </si>
-  <si>
-    <t>0.0132,0.6733,0.8440,0.0056</t>
-  </si>
-  <si>
-    <t>0.0231,0.7468,0.6563,0.0125</t>
-  </si>
-  <si>
-    <t>0.0151,0.1781,0.9505,0.0065</t>
-  </si>
-  <si>
-    <t>0.0029,0.8768,0.8279,0.0009</t>
-  </si>
-  <si>
-    <t>0.0091,0.8612,0.6896,0.0034</t>
-  </si>
-  <si>
-    <t>0.9854,0.0085,0.0010,0.0038</t>
-  </si>
-  <si>
-    <t>0.9823,0.0132,0.0012,0.0031</t>
-  </si>
-  <si>
-    <t>0.9883,0.0072,0.0007,0.0024</t>
-  </si>
-  <si>
-    <t>0.9733,0.0224,0.0027,0.0035</t>
-  </si>
-  <si>
-    <t>0.9873,0.0066,0.0011,0.0032</t>
-  </si>
-  <si>
-    <t>0.9898,0.0064,0.0007,0.0022</t>
-  </si>
-  <si>
-    <t>0.9836,0.0090,0.0012,0.0039</t>
-  </si>
-  <si>
-    <t>0.9772,0.0146,0.0019,0.0046</t>
-  </si>
-  <si>
-    <t>0.9824,0.0086,0.0015,0.0053</t>
-  </si>
-  <si>
-    <t>0.9790,0.0099,0.0015,0.0074</t>
-  </si>
-  <si>
-    <t>0.9860,0.0059,0.0011,0.0046</t>
-  </si>
-  <si>
-    <t>0.9921,0.0036,0.0004,0.0029</t>
-  </si>
-  <si>
-    <t>0.9795,0.0093,0.0015,0.0068</t>
-  </si>
-  <si>
-    <t>0.9846,0.0083,0.0010,0.0044</t>
-  </si>
-  <si>
-    <t>0.9837,0.0082,0.0013,0.0042</t>
-  </si>
-  <si>
-    <t>0.9882,0.0041,0.0005,0.0055</t>
-  </si>
-  <si>
-    <t>0.0055,0.0206,0.9874,0.0062</t>
-  </si>
-  <si>
-    <t>0.1477,0.1620,0.7193,0.0421</t>
-  </si>
-  <si>
-    <t>0.2339,0.6383,0.1848,0.0774</t>
-  </si>
-  <si>
-    <t>0.3246,0.0855,0.5805,0.0952</t>
-  </si>
-  <si>
-    <t>0.1202,0.8910,0.0219,0.0033</t>
-  </si>
-  <si>
-    <t>0.0917,0.9112,0.0196,0.0029</t>
-  </si>
-  <si>
-    <t>0.4141,0.6002,0.0421,0.0072</t>
-  </si>
-  <si>
-    <t>0.4323,0.6364,0.0265,0.0063</t>
-  </si>
-  <si>
-    <t>0.1409,0.8479,0.0385,0.0049</t>
-  </si>
-  <si>
-    <t>0.0346,0.9546,0.0207,0.0022</t>
-  </si>
-  <si>
-    <t>0.7564,0.3349,0.0133,0.0050</t>
-  </si>
-  <si>
-    <t>0.3642,0.4451,0.1933,0.2227</t>
-  </si>
-  <si>
-    <t>0.1876,0.0934,0.7390,0.0568</t>
-  </si>
-  <si>
-    <t>0.5051,0.4425,0.1159,0.0777</t>
-  </si>
-  <si>
-    <t>0.1703,0.6275,0.2731,0.0416</t>
-  </si>
-  <si>
-    <t>0.6029,0.2722,0.1563,0.0644</t>
-  </si>
-  <si>
-    <t>0.0036,0.9882,0.0136,0.0038</t>
-  </si>
-  <si>
-    <t>0.0289,0.9261,0.1024,0.0090</t>
-  </si>
-  <si>
-    <t>0.0563,0.8709,0.1256,0.0137</t>
-  </si>
-  <si>
-    <t>0.0035,0.9863,0.0415,0.0014</t>
-  </si>
-  <si>
-    <t>0.1431,0.8195,0.0756,0.0095</t>
-  </si>
-  <si>
-    <t>0.8031,0.1812,0.0466,0.0103</t>
-  </si>
-  <si>
-    <t>0.8719,0.1722,0.0126,0.0063</t>
-  </si>
-  <si>
-    <t>0.9481,0.0340,0.0107,0.0065</t>
-  </si>
-  <si>
-    <t>0.9791,0.0156,0.0016,0.0032</t>
-  </si>
-  <si>
-    <t>0.9666,0.0142,0.0035,0.0108</t>
-  </si>
-  <si>
-    <t>0.9703,0.0142,0.0038,0.0074</t>
-  </si>
-  <si>
-    <t>0.9796,0.0103,0.0023,0.0054</t>
-  </si>
-  <si>
-    <t>0.9573,0.0231,0.0046,0.0110</t>
-  </si>
-  <si>
-    <t>0.9808,0.0082,0.0024,0.0063</t>
-  </si>
-  <si>
-    <t>0.9518,0.0258,0.0097,0.0099</t>
-  </si>
-  <si>
-    <t>0.0179,0.6464,0.7924,0.0050</t>
-  </si>
-  <si>
-    <t>0.0181,0.8493,0.5414,0.0123</t>
-  </si>
-  <si>
-    <t>0.0332,0.4210,0.8176,0.0119</t>
-  </si>
-  <si>
-    <t>0.0384,0.3158,0.8377,0.0084</t>
-  </si>
-  <si>
-    <t>0.6775,0.1677,0.1315,0.0871</t>
-  </si>
-  <si>
-    <t>0.4834,0.1137,0.4423,0.0365</t>
-  </si>
-  <si>
-    <t>0.3882,0.0234,0.6498,0.0523</t>
-  </si>
-  <si>
-    <t>0.6235,0.2342,0.1562,0.1037</t>
-  </si>
-  <si>
-    <t>0.0749,0.0191,0.0070,0.9587</t>
-  </si>
-  <si>
-    <t>0.0032,0.0265,0.0014,0.9964</t>
-  </si>
-  <si>
-    <t>0.0087,0.0570,0.0047,0.9900</t>
-  </si>
-  <si>
-    <t>0.0432,0.0409,0.0035,0.9765</t>
-  </si>
-  <si>
-    <t>0.0311,0.7297,0.6281,0.0187</t>
-  </si>
-  <si>
-    <t>0.9415,0.0418,0.0090,0.0112</t>
-  </si>
-  <si>
-    <t>0.8986,0.1075,0.0124,0.0099</t>
-  </si>
-  <si>
-    <t>0.9711,0.0146,0.0032,0.0091</t>
-  </si>
-  <si>
-    <t>0.9104,0.1003,0.0107,0.0086</t>
-  </si>
-  <si>
-    <t>0.9603,0.0230,0.0054,0.0107</t>
-  </si>
-  <si>
-    <t>0.8076,0.0333,0.1182,0.0474</t>
-  </si>
-  <si>
-    <t>0.9844,0.0081,0.0010,0.0047</t>
-  </si>
-  <si>
-    <t>0.3346,0.4594,0.2611,0.0511</t>
-  </si>
-  <si>
-    <t>0.6534,0.0179,0.0230,0.3875</t>
-  </si>
-  <si>
-    <t>0.9198,0.0285,0.0093,0.0343</t>
-  </si>
-  <si>
-    <t>0.5924,0.4210,0.0535,0.0221</t>
-  </si>
-  <si>
-    <t>0.8843,0.0722,0.0186,0.0249</t>
-  </si>
-  <si>
-    <t>0.8656,0.1268,0.0250,0.0141</t>
-  </si>
-  <si>
-    <t>0.6067,0.2892,0.1208,0.0385</t>
-  </si>
-  <si>
-    <t>0.6288,0.2824,0.1403,0.0340</t>
-  </si>
-  <si>
-    <t>0.6120,0.3453,0.0815,0.0170</t>
-  </si>
-  <si>
-    <t>0.9807,0.0073,0.0016,0.0073</t>
-  </si>
-  <si>
-    <t>0.9878,0.0054,0.0009,0.0038</t>
-  </si>
-  <si>
-    <t>0.9809,0.0118,0.0016,0.0043</t>
-  </si>
-  <si>
-    <t>0.9820,0.0061,0.0013,0.0083</t>
-  </si>
-  <si>
-    <t>0.9810,0.0070,0.0012,0.0073</t>
-  </si>
-  <si>
-    <t>0.9799,0.0108,0.0017,0.0061</t>
-  </si>
-  <si>
-    <t>0.9870,0.0058,0.0010,0.0037</t>
-  </si>
-  <si>
-    <t>0.9792,0.0136,0.0017,0.0053</t>
-  </si>
-  <si>
-    <t>0.8126,0.2343,0.0231,0.0098</t>
-  </si>
-  <si>
-    <t>0.8974,0.1303,0.0102,0.0052</t>
-  </si>
-  <si>
-    <t>0.7138,0.3479,0.0306,0.0099</t>
-  </si>
-  <si>
-    <t>0.7903,0.1693,0.0601,0.0202</t>
-  </si>
-  <si>
-    <t>0.9443,0.0548,0.0065,0.0058</t>
-  </si>
-  <si>
-    <t>0.9549,0.0342,0.0070,0.0039</t>
-  </si>
-  <si>
-    <t>0.9382,0.0629,0.0072,0.0047</t>
-  </si>
-  <si>
-    <t>0.8502,0.1512,0.0263,0.0106</t>
-  </si>
-  <si>
-    <t>0.0353,0.1762,0.9228,0.0051</t>
-  </si>
-  <si>
-    <t>0.9640,0.0313,0.0042,0.0058</t>
-  </si>
-  <si>
-    <t>0.0258,0.0722,0.9270,0.0295</t>
-  </si>
-  <si>
-    <t>0.0247,0.2968,0.8833,0.0140</t>
-  </si>
-  <si>
-    <t>0.0671,0.0740,0.8986,0.0174</t>
-  </si>
-  <si>
-    <t>0.0439,0.3703,0.8225,0.0158</t>
-  </si>
-  <si>
-    <t>0.0655,0.0386,0.9104,0.0184</t>
-  </si>
-  <si>
-    <t>0.0190,0.0139,0.9756,0.0063</t>
-  </si>
-  <si>
-    <t>0.0423,0.2031,0.8865,0.0113</t>
-  </si>
-  <si>
-    <t>0.2640,0.3435,0.4523,0.0294</t>
-  </si>
-  <si>
-    <t>0.1227,0.1117,0.8227,0.0196</t>
-  </si>
-  <si>
-    <t>0.2886,0.1579,0.6034,0.0549</t>
-  </si>
-  <si>
-    <t>0.1901,0.5610,0.2870,0.0101</t>
-  </si>
-  <si>
-    <t>0.2459,0.5597,0.2566,0.0218</t>
-  </si>
-  <si>
-    <t>0.2154,0.1338,0.6918,0.0296</t>
-  </si>
-  <si>
-    <t>0.1611,0.6042,0.3356,0.0230</t>
-  </si>
-  <si>
-    <t>0.4938,0.1300,0.4104,0.0685</t>
-  </si>
-  <si>
-    <t>0.9044,0.1059,0.0105,0.0051</t>
-  </si>
-  <si>
-    <t>0.9453,0.0664,0.0036,0.0049</t>
-  </si>
-  <si>
-    <t>0.9721,0.0229,0.0026,0.0041</t>
-  </si>
-  <si>
-    <t>0.9738,0.0191,0.0030,0.0038</t>
-  </si>
-  <si>
-    <t>0.9710,0.0209,0.0032,0.0044</t>
-  </si>
-  <si>
-    <t>0.4284,0.3653,0.2365,0.0278</t>
-  </si>
-  <si>
-    <t>0.5106,0.1486,0.3691,0.0593</t>
-  </si>
-  <si>
-    <t>0.4028,0.1471,0.3213,0.2624</t>
-  </si>
-  <si>
-    <t>0.4288,0.3498,0.1660,0.2678</t>
-  </si>
-  <si>
-    <t>0.4802,0.0963,0.4396,0.0935</t>
-  </si>
-  <si>
-    <t>0.1762,0.1394,0.6616,0.1157</t>
-  </si>
-  <si>
-    <t>0.0412,0.2504,0.8547,0.0248</t>
-  </si>
-  <si>
-    <t>0.0188,0.0730,0.9546,0.0127</t>
-  </si>
-  <si>
-    <t>0.0459,0.5306,0.7430,0.0206</t>
-  </si>
-  <si>
-    <t>0.0282,0.6928,0.6844,0.0127</t>
-  </si>
-  <si>
-    <t>0.9876,0.0064,0.0007,0.0037</t>
-  </si>
-  <si>
-    <t>0.9822,0.0120,0.0017,0.0030</t>
-  </si>
-  <si>
-    <t>0.9859,0.0079,0.0011,0.0034</t>
-  </si>
-  <si>
-    <t>0.9692,0.0230,0.0035,0.0038</t>
-  </si>
-  <si>
-    <t>0.9795,0.0118,0.0016,0.0049</t>
-  </si>
-  <si>
-    <t>0.9773,0.0150,0.0026,0.0035</t>
-  </si>
-  <si>
-    <t>0.9883,0.0053,0.0007,0.0041</t>
-  </si>
-  <si>
-    <t>0.9856,0.0059,0.0011,0.0057</t>
-  </si>
-  <si>
-    <t>0.4255,0.2854,0.3149,0.0225</t>
-  </si>
-  <si>
-    <t>0.3746,0.5359,0.1432,0.0223</t>
-  </si>
-  <si>
-    <t>0.9066,0.0364,0.0391,0.0184</t>
-  </si>
-  <si>
-    <t>0.0169,0.0801,0.9568,0.0108</t>
-  </si>
-  <si>
-    <t>0.0140,0.0958,0.9515,0.0151</t>
-  </si>
-  <si>
-    <t>0.0948,0.1780,0.7887,0.0256</t>
-  </si>
-  <si>
-    <t>0.0026,0.0432,0.9919,0.0021</t>
-  </si>
-  <si>
-    <t>0.1229,0.4200,0.5756,0.0267</t>
-  </si>
-  <si>
-    <t>0.0070,0.0624,0.9778,0.0063</t>
-  </si>
-  <si>
-    <t>0.0351,0.0597,0.9270,0.0255</t>
-  </si>
-  <si>
-    <t>0.1765,0.4041,0.4677,0.0305</t>
-  </si>
-  <si>
-    <t>0.4656,0.1775,0.3512,0.1489</t>
-  </si>
-  <si>
-    <t>0.5040,0.0419,0.4034,0.0932</t>
-  </si>
-  <si>
-    <t>0.5937,0.2332,0.1650,0.1220</t>
-  </si>
-  <si>
-    <t>0.9712,0.0174,0.0038,0.0056</t>
-  </si>
-  <si>
-    <t>0.9871,0.0074,0.0009,0.0033</t>
-  </si>
-  <si>
-    <t>0.9839,0.0088,0.0016,0.0036</t>
-  </si>
-  <si>
-    <t>0.9803,0.0144,0.0015,0.0031</t>
-  </si>
-  <si>
-    <t>0.9793,0.0109,0.0016,0.0056</t>
-  </si>
-  <si>
-    <t>0.9840,0.0086,0.0017,0.0038</t>
-  </si>
-  <si>
-    <t>0.9857,0.0063,0.0010,0.0042</t>
-  </si>
-  <si>
-    <t>0.9905,0.0056,0.0004,0.0027</t>
-  </si>
-  <si>
-    <t>0.1206,0.2149,0.7201,0.0141</t>
-  </si>
-  <si>
-    <t>0.0154,0.1583,0.9470,0.0104</t>
-  </si>
-  <si>
-    <t>0.0233,0.2592,0.9062,0.0070</t>
-  </si>
-  <si>
-    <t>0.1427,0.3803,0.5293,0.0297</t>
-  </si>
-  <si>
-    <t>0.0826,0.1225,0.8317,0.0287</t>
-  </si>
-  <si>
-    <t>0.1761,0.0535,0.6514,0.2078</t>
-  </si>
-  <si>
-    <t>0.2628,0.0825,0.3017,0.4442</t>
-  </si>
-  <si>
-    <t>0.0335,0.0880,0.8812,0.0664</t>
-  </si>
-  <si>
-    <t>0.8591,0.0305,0.0282,0.0922</t>
-  </si>
-  <si>
-    <t>0.0207,0.0351,0.0039,0.9865</t>
-  </si>
-  <si>
-    <t>0.2322,0.0492,0.0096,0.8535</t>
-  </si>
-  <si>
-    <t>0.0405,0.0192,0.0031,0.9794</t>
-  </si>
-  <si>
-    <t>0.0133,0.0148,0.0017,0.9923</t>
-  </si>
-  <si>
-    <t>0.6742,0.2175,0.1165,0.0489</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.6767,0.2032,0.0478,0.2096</t>
+  </si>
+  <si>
+    <t>0.0356,0.0310,0.0028,0.9833</t>
+  </si>
+  <si>
+    <t>0.7629,0.1225,0.0290,0.1298</t>
+  </si>
+  <si>
+    <t>0.1715,0.0506,0.0047,0.9109</t>
+  </si>
+  <si>
+    <t>0.9887,0.0046,0.0006,0.0040</t>
+  </si>
+  <si>
+    <t>0.9898,0.0050,0.0006,0.0033</t>
+  </si>
+  <si>
+    <t>0.9718,0.0173,0.0036,0.0059</t>
+  </si>
+  <si>
+    <t>0.9854,0.0066,0.0013,0.0041</t>
+  </si>
+  <si>
+    <t>0.9852,0.0085,0.0012,0.0030</t>
+  </si>
+  <si>
+    <t>0.9745,0.0240,0.0024,0.0028</t>
+  </si>
+  <si>
+    <t>0.9856,0.0079,0.0012,0.0034</t>
+  </si>
+  <si>
+    <t>0.9890,0.0050,0.0007,0.0035</t>
+  </si>
+  <si>
+    <t>0.2243,0.5120,0.3486,0.0315</t>
+  </si>
+  <si>
+    <t>0.2128,0.3874,0.4411,0.0135</t>
+  </si>
+  <si>
+    <t>0.0821,0.0515,0.9078,0.0136</t>
+  </si>
+  <si>
+    <t>0.4399,0.3474,0.2413,0.0586</t>
+  </si>
+  <si>
+    <t>0.3643,0.4193,0.2781,0.0530</t>
+  </si>
+  <si>
+    <t>0.0416,0.9417,0.0345,0.0023</t>
+  </si>
+  <si>
+    <t>0.1890,0.8101,0.0433,0.0060</t>
+  </si>
+  <si>
+    <t>0.6640,0.3742,0.0409,0.0110</t>
+  </si>
+  <si>
+    <t>0.1216,0.8888,0.0203,0.0034</t>
+  </si>
+  <si>
+    <t>0.0222,0.9582,0.0458,0.0010</t>
+  </si>
+  <si>
+    <t>0.4818,0.0642,0.3486,0.1358</t>
+  </si>
+  <si>
+    <t>0.2158,0.3496,0.4769,0.0425</t>
+  </si>
+  <si>
+    <t>0.0159,0.0729,0.9549,0.0129</t>
+  </si>
+  <si>
+    <t>0.2231,0.0359,0.6895,0.1281</t>
+  </si>
+  <si>
+    <t>0.1041,0.2077,0.7613,0.0299</t>
+  </si>
+  <si>
+    <t>0.3725,0.3139,0.3561,0.0977</t>
+  </si>
+  <si>
+    <t>0.0611,0.0557,0.8880,0.0454</t>
+  </si>
+  <si>
+    <t>0.8092,0.1932,0.0358,0.0129</t>
+  </si>
+  <si>
+    <t>0.2865,0.4424,0.3118,0.0189</t>
+  </si>
+  <si>
+    <t>0.0795,0.3021,0.7911,0.0240</t>
+  </si>
+  <si>
+    <t>0.0324,0.9259,0.0834,0.0035</t>
+  </si>
+  <si>
+    <t>0.8888,0.0858,0.0189,0.0244</t>
+  </si>
+  <si>
+    <t>0.7423,0.2310,0.0624,0.0364</t>
+  </si>
+  <si>
+    <t>0.7957,0.2451,0.0204,0.0046</t>
+  </si>
+  <si>
+    <t>0.1469,0.7866,0.1025,0.0105</t>
+  </si>
+  <si>
+    <t>0.0393,0.3489,0.8278,0.0152</t>
+  </si>
+  <si>
+    <t>0.0168,0.1172,0.8780,0.0490</t>
+  </si>
+  <si>
+    <t>0.0570,0.3597,0.7909,0.0201</t>
+  </si>
+  <si>
+    <t>0.1317,0.0277,0.7299,0.1423</t>
+  </si>
+  <si>
+    <t>0.0428,0.3195,0.8368,0.0079</t>
+  </si>
+  <si>
+    <t>0.0184,0.8630,0.4227,0.0077</t>
+  </si>
+  <si>
+    <t>0.0345,0.1881,0.9007,0.0147</t>
+  </si>
+  <si>
+    <t>0.2293,0.5657,0.0712,0.3418</t>
+  </si>
+  <si>
+    <t>0.0293,0.9413,0.0348,0.0147</t>
+  </si>
+  <si>
+    <t>0.0282,0.9341,0.0654,0.0064</t>
+  </si>
+  <si>
+    <t>0.0040,0.9874,0.0155,0.0022</t>
+  </si>
+  <si>
+    <t>0.0134,0.2868,0.9083,0.0105</t>
+  </si>
+  <si>
+    <t>0.0075,0.4098,0.9461,0.0020</t>
+  </si>
+  <si>
+    <t>0.0961,0.1299,0.8095,0.0731</t>
+  </si>
+  <si>
+    <t>0.0810,0.0634,0.8946,0.0203</t>
+  </si>
+  <si>
+    <t>0.0562,0.2688,0.7644,0.0610</t>
+  </si>
+  <si>
+    <t>0.0327,0.1795,0.9036,0.0086</t>
+  </si>
+  <si>
+    <t>0.9608,0.0430,0.0038,0.0029</t>
+  </si>
+  <si>
+    <t>0.9798,0.0122,0.0019,0.0036</t>
+  </si>
+  <si>
+    <t>0.9694,0.0169,0.0027,0.0091</t>
+  </si>
+  <si>
+    <t>0.0791,0.4379,0.7030,0.0354</t>
+  </si>
+  <si>
+    <t>0.9709,0.0202,0.0038,0.0047</t>
+  </si>
+  <si>
+    <t>0.9722,0.0251,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.9593,0.0296,0.0057,0.0044</t>
+  </si>
+  <si>
+    <t>0.0053,0.8849,0.7539,0.0025</t>
+  </si>
+  <si>
+    <t>0.0080,0.3402,0.9495,0.0027</t>
+  </si>
+  <si>
+    <t>0.0066,0.2638,0.9588,0.0035</t>
+  </si>
+  <si>
+    <t>0.0044,0.8734,0.8093,0.0036</t>
+  </si>
+  <si>
+    <t>0.0086,0.1643,0.9641,0.0040</t>
+  </si>
+  <si>
+    <t>0.0255,0.9389,0.0729,0.0024</t>
+  </si>
+  <si>
+    <t>0.0046,0.9905,0.0070,0.0007</t>
+  </si>
+  <si>
+    <t>0.5298,0.1915,0.3218,0.0235</t>
+  </si>
+  <si>
+    <t>0.5797,0.1581,0.3011,0.0215</t>
+  </si>
+  <si>
+    <t>0.1274,0.4696,0.5270,0.0247</t>
+  </si>
+  <si>
+    <t>0.0102,0.8716,0.6272,0.0067</t>
+  </si>
+  <si>
+    <t>0.0253,0.7575,0.6035,0.0119</t>
+  </si>
+  <si>
+    <t>0.0049,0.9250,0.6104,0.0020</t>
+  </si>
+  <si>
+    <t>0.0078,0.7772,0.8516,0.0035</t>
+  </si>
+  <si>
+    <t>0.1871,0.0279,0.0217,0.8790</t>
+  </si>
+  <si>
+    <t>0.0379,0.0253,0.0059,0.9765</t>
+  </si>
+  <si>
+    <t>0.0139,0.0222,0.0030,0.9904</t>
+  </si>
+  <si>
+    <t>0.0957,0.0328,0.0087,0.9467</t>
+  </si>
+  <si>
+    <t>0.0706,0.0728,0.0074,0.9575</t>
+  </si>
+  <si>
+    <t>0.0325,0.0200,0.0030,0.9835</t>
+  </si>
+  <si>
+    <t>0.0077,0.7946,0.8167,0.0026</t>
+  </si>
+  <si>
+    <t>0.0100,0.6395,0.8736,0.0031</t>
+  </si>
+  <si>
+    <t>0.0136,0.5995,0.8663,0.0048</t>
+  </si>
+  <si>
+    <t>0.0101,0.4693,0.9166,0.0039</t>
+  </si>
+  <si>
+    <t>0.0037,0.9269,0.6674,0.0015</t>
+  </si>
+  <si>
+    <t>0.0135,0.7768,0.7443,0.0064</t>
+  </si>
+  <si>
+    <t>0.9808,0.0094,0.0022,0.0044</t>
+  </si>
+  <si>
+    <t>0.9864,0.0078,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.9813,0.0123,0.0019,0.0031</t>
+  </si>
+  <si>
+    <t>0.9883,0.0070,0.0008,0.0027</t>
+  </si>
+  <si>
+    <t>0.9635,0.0294,0.0042,0.0049</t>
+  </si>
+  <si>
+    <t>0.9848,0.0089,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.9577,0.0347,0.0053,0.0051</t>
+  </si>
+  <si>
+    <t>0.9901,0.0054,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9868,0.0071,0.0011,0.0036</t>
+  </si>
+  <si>
+    <t>0.9789,0.0135,0.0024,0.0032</t>
+  </si>
+  <si>
+    <t>0.9923,0.0039,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9902,0.0049,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.9899,0.0044,0.0008,0.0032</t>
+  </si>
+  <si>
+    <t>0.9893,0.0049,0.0006,0.0036</t>
+  </si>
+  <si>
+    <t>0.9861,0.0076,0.0008,0.0040</t>
+  </si>
+  <si>
+    <t>0.9858,0.0066,0.0010,0.0049</t>
+  </si>
+  <si>
+    <t>0.0092,0.0142,0.9807,0.0109</t>
+  </si>
+  <si>
+    <t>0.0789,0.1176,0.8833,0.0168</t>
+  </si>
+  <si>
+    <t>0.3089,0.5533,0.1764,0.0751</t>
+  </si>
+  <si>
+    <t>0.1186,0.0490,0.8366,0.0577</t>
+  </si>
+  <si>
+    <t>0.1901,0.8390,0.0232,0.0047</t>
+  </si>
+  <si>
+    <t>0.1206,0.8662,0.0375,0.0049</t>
+  </si>
+  <si>
+    <t>0.3084,0.7677,0.0151,0.0051</t>
+  </si>
+  <si>
+    <t>0.4276,0.6150,0.0413,0.0089</t>
+  </si>
+  <si>
+    <t>0.0546,0.9400,0.0148,0.0024</t>
+  </si>
+  <si>
+    <t>0.0606,0.9309,0.0225,0.0022</t>
+  </si>
+  <si>
+    <t>0.7693,0.2787,0.0247,0.0084</t>
+  </si>
+  <si>
+    <t>0.5742,0.1496,0.2884,0.0764</t>
+  </si>
+  <si>
+    <t>0.2335,0.1135,0.6761,0.0362</t>
+  </si>
+  <si>
+    <t>0.1814,0.7361,0.0883,0.0837</t>
+  </si>
+  <si>
+    <t>0.2336,0.2890,0.5133,0.0515</t>
+  </si>
+  <si>
+    <t>0.5715,0.0892,0.0828,0.3682</t>
+  </si>
+  <si>
+    <t>0.0092,0.9825,0.0136,0.0011</t>
+  </si>
+  <si>
+    <t>0.0069,0.9812,0.0164,0.0058</t>
+  </si>
+  <si>
+    <t>0.2328,0.7198,0.0590,0.0605</t>
+  </si>
+  <si>
+    <t>0.0049,0.9879,0.0144,0.0019</t>
+  </si>
+  <si>
+    <t>0.0443,0.9194,0.0649,0.0023</t>
+  </si>
+  <si>
+    <t>0.9277,0.0748,0.0077,0.0059</t>
+  </si>
+  <si>
+    <t>0.8536,0.1663,0.0182,0.0059</t>
+  </si>
+  <si>
+    <t>0.9188,0.0670,0.0118,0.0113</t>
+  </si>
+  <si>
+    <t>0.9795,0.0101,0.0022,0.0063</t>
+  </si>
+  <si>
+    <t>0.9709,0.0164,0.0035,0.0063</t>
+  </si>
+  <si>
+    <t>0.9478,0.0356,0.0090,0.0068</t>
+  </si>
+  <si>
+    <t>0.9842,0.0067,0.0016,0.0050</t>
+  </si>
+  <si>
+    <t>0.9404,0.0375,0.0104,0.0124</t>
+  </si>
+  <si>
+    <t>0.9390,0.0502,0.0078,0.0056</t>
+  </si>
+  <si>
+    <t>0.9832,0.0095,0.0014,0.0044</t>
+  </si>
+  <si>
+    <t>0.0158,0.6018,0.8304,0.0058</t>
+  </si>
+  <si>
+    <t>0.0116,0.8900,0.4920,0.0059</t>
+  </si>
+  <si>
+    <t>0.0291,0.3332,0.8707,0.0065</t>
+  </si>
+  <si>
+    <t>0.0230,0.4135,0.8674,0.0066</t>
+  </si>
+  <si>
+    <t>0.4121,0.3456,0.3116,0.0988</t>
+  </si>
+  <si>
+    <t>0.6731,0.1519,0.1772,0.0795</t>
+  </si>
+  <si>
+    <t>0.6032,0.0745,0.3358,0.0420</t>
+  </si>
+  <si>
+    <t>0.6097,0.0928,0.2809,0.0808</t>
+  </si>
+  <si>
+    <t>0.0965,0.0765,0.0179,0.9332</t>
+  </si>
+  <si>
+    <t>0.0020,0.0137,0.0007,0.9981</t>
+  </si>
+  <si>
+    <t>0.0056,0.0642,0.0052,0.9906</t>
+  </si>
+  <si>
+    <t>0.1017,0.0221,0.0056,0.9512</t>
+  </si>
+  <si>
+    <t>0.0083,0.9146,0.4731,0.0059</t>
+  </si>
+  <si>
+    <t>0.9831,0.0094,0.0018,0.0042</t>
+  </si>
+  <si>
+    <t>0.3040,0.7155,0.0396,0.0139</t>
+  </si>
+  <si>
+    <t>0.9672,0.0112,0.0032,0.0176</t>
+  </si>
+  <si>
+    <t>0.8472,0.1505,0.0259,0.0100</t>
+  </si>
+  <si>
+    <t>0.9655,0.0194,0.0033,0.0116</t>
+  </si>
+  <si>
+    <t>0.9190,0.0224,0.0136,0.0400</t>
+  </si>
+  <si>
+    <t>0.9746,0.0085,0.0022,0.0117</t>
+  </si>
+  <si>
+    <t>0.3752,0.3566,0.3376,0.0535</t>
+  </si>
+  <si>
+    <t>0.4403,0.0146,0.0101,0.6964</t>
+  </si>
+  <si>
+    <t>0.8683,0.0197,0.0241,0.0826</t>
+  </si>
+  <si>
+    <t>0.7434,0.2087,0.0782,0.0420</t>
+  </si>
+  <si>
+    <t>0.7868,0.1731,0.0533,0.0258</t>
+  </si>
+  <si>
+    <t>0.6922,0.2634,0.0825,0.0160</t>
+  </si>
+  <si>
+    <t>0.3113,0.4960,0.2170,0.0176</t>
+  </si>
+  <si>
+    <t>0.9059,0.0481,0.0234,0.0221</t>
+  </si>
+  <si>
+    <t>0.6272,0.3139,0.1034,0.0188</t>
+  </si>
+  <si>
+    <t>0.9755,0.0108,0.0016,0.0104</t>
+  </si>
+  <si>
+    <t>0.9742,0.0165,0.0025,0.0053</t>
+  </si>
+  <si>
+    <t>0.9794,0.0130,0.0018,0.0038</t>
+  </si>
+  <si>
+    <t>0.9723,0.0122,0.0043,0.0084</t>
+  </si>
+  <si>
+    <t>0.9812,0.0111,0.0016,0.0044</t>
+  </si>
+  <si>
+    <t>0.9764,0.0122,0.0026,0.0067</t>
+  </si>
+  <si>
+    <t>0.9836,0.0080,0.0013,0.0049</t>
+  </si>
+  <si>
+    <t>0.9843,0.0072,0.0008,0.0062</t>
+  </si>
+  <si>
+    <t>0.3337,0.7386,0.0211,0.0080</t>
+  </si>
+  <si>
+    <t>0.9068,0.0966,0.0145,0.0056</t>
+  </si>
+  <si>
+    <t>0.8893,0.1495,0.0095,0.0059</t>
+  </si>
+  <si>
+    <t>0.7327,0.2603,0.0550,0.0101</t>
+  </si>
+  <si>
+    <t>0.8997,0.1279,0.0096,0.0057</t>
+  </si>
+  <si>
+    <t>0.9541,0.0319,0.0068,0.0073</t>
+  </si>
+  <si>
+    <t>0.9756,0.0142,0.0028,0.0059</t>
+  </si>
+  <si>
+    <t>0.7864,0.1921,0.0460,0.0096</t>
+  </si>
+  <si>
+    <t>0.1310,0.2809,0.6870,0.0117</t>
+  </si>
+  <si>
+    <t>0.9428,0.0313,0.0108,0.0123</t>
+  </si>
+  <si>
+    <t>0.0168,0.0281,0.9791,0.0042</t>
+  </si>
+  <si>
+    <t>0.0197,0.4098,0.8821,0.0087</t>
+  </si>
+  <si>
+    <t>0.1153,0.0946,0.7219,0.1474</t>
+  </si>
+  <si>
+    <t>0.0268,0.3400,0.8850,0.0087</t>
+  </si>
+  <si>
+    <t>0.0199,0.0312,0.9692,0.0089</t>
+  </si>
+  <si>
+    <t>0.0237,0.0237,0.9701,0.0067</t>
+  </si>
+  <si>
+    <t>0.0457,0.1091,0.9125,0.0131</t>
+  </si>
+  <si>
+    <t>0.4449,0.3806,0.2381,0.0321</t>
+  </si>
+  <si>
+    <t>0.4917,0.2458,0.2649,0.0280</t>
+  </si>
+  <si>
+    <t>0.1290,0.6533,0.3011,0.0139</t>
+  </si>
+  <si>
+    <t>0.1435,0.4372,0.5065,0.0123</t>
+  </si>
+  <si>
+    <t>0.1378,0.4932,0.4668,0.0195</t>
+  </si>
+  <si>
+    <t>0.3158,0.3545,0.3091,0.0173</t>
+  </si>
+  <si>
+    <t>0.2152,0.6776,0.1658,0.0390</t>
+  </si>
+  <si>
+    <t>0.6250,0.2270,0.1611,0.0633</t>
+  </si>
+  <si>
+    <t>0.8389,0.1864,0.0187,0.0048</t>
+  </si>
+  <si>
+    <t>0.9612,0.0417,0.0031,0.0044</t>
+  </si>
+  <si>
+    <t>0.9194,0.0800,0.0118,0.0062</t>
+  </si>
+  <si>
+    <t>0.9809,0.0120,0.0017,0.0043</t>
+  </si>
+  <si>
+    <t>0.9628,0.0352,0.0037,0.0038</t>
+  </si>
+  <si>
+    <t>0.2066,0.6846,0.1519,0.0247</t>
+  </si>
+  <si>
+    <t>0.7211,0.1740,0.0950,0.0438</t>
+  </si>
+  <si>
+    <t>0.5631,0.2680,0.1838,0.0376</t>
+  </si>
+  <si>
+    <t>0.4496,0.0718,0.0719,0.5836</t>
+  </si>
+  <si>
+    <t>0.4505,0.1274,0.4156,0.1574</t>
+  </si>
+  <si>
+    <t>0.2483,0.1762,0.6426,0.0459</t>
+  </si>
+  <si>
+    <t>0.0679,0.3584,0.7133,0.0429</t>
+  </si>
+  <si>
+    <t>0.0348,0.2734,0.8884,0.0105</t>
+  </si>
+  <si>
+    <t>0.0191,0.0450,0.9662,0.0104</t>
+  </si>
+  <si>
+    <t>0.0397,0.2367,0.8570,0.0161</t>
+  </si>
+  <si>
+    <t>0.9814,0.0088,0.0016,0.0051</t>
+  </si>
+  <si>
+    <t>0.9866,0.0073,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9783,0.0135,0.0025,0.0031</t>
+  </si>
+  <si>
+    <t>0.9834,0.0113,0.0016,0.0023</t>
+  </si>
+  <si>
+    <t>0.9831,0.0112,0.0014,0.0030</t>
+  </si>
+  <si>
+    <t>0.9883,0.0057,0.0008,0.0037</t>
+  </si>
+  <si>
+    <t>0.9910,0.0046,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9802,0.0116,0.0020,0.0037</t>
+  </si>
+  <si>
+    <t>0.2013,0.0542,0.8041,0.0264</t>
+  </si>
+  <si>
+    <t>0.5759,0.3172,0.1524,0.0316</t>
+  </si>
+  <si>
+    <t>0.9036,0.0779,0.0177,0.0130</t>
+  </si>
+  <si>
+    <t>0.0088,0.0353,0.9843,0.0043</t>
+  </si>
+  <si>
+    <t>0.0071,0.0726,0.9801,0.0034</t>
+  </si>
+  <si>
+    <t>0.1119,0.1330,0.8029,0.0187</t>
+  </si>
+  <si>
+    <t>0.0080,0.0190,0.9852,0.0059</t>
+  </si>
+  <si>
+    <t>0.2767,0.2547,0.4872,0.0216</t>
+  </si>
+  <si>
+    <t>0.0046,0.0276,0.9897,0.0039</t>
+  </si>
+  <si>
+    <t>0.0466,0.1485,0.8578,0.0300</t>
+  </si>
+  <si>
+    <t>0.1260,0.1235,0.7795,0.0674</t>
+  </si>
+  <si>
+    <t>0.3777,0.1241,0.5110,0.0573</t>
+  </si>
+  <si>
+    <t>0.4796,0.1788,0.2815,0.2383</t>
+  </si>
+  <si>
+    <t>0.4621,0.1003,0.2875,0.2608</t>
+  </si>
+  <si>
+    <t>0.9829,0.0107,0.0013,0.0038</t>
+  </si>
+  <si>
+    <t>0.9702,0.0269,0.0027,0.0029</t>
+  </si>
+  <si>
+    <t>0.9908,0.0050,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9806,0.0107,0.0015,0.0058</t>
+  </si>
+  <si>
+    <t>0.9745,0.0156,0.0034,0.0046</t>
+  </si>
+  <si>
+    <t>0.9885,0.0054,0.0007,0.0041</t>
+  </si>
+  <si>
+    <t>0.9860,0.0095,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.9863,0.0081,0.0010,0.0032</t>
+  </si>
+  <si>
+    <t>0.0967,0.3998,0.6599,0.0265</t>
+  </si>
+  <si>
+    <t>0.0239,0.3811,0.8678,0.0067</t>
+  </si>
+  <si>
+    <t>0.0150,0.1793,0.9538,0.0051</t>
+  </si>
+  <si>
+    <t>0.1799,0.3356,0.5256,0.0550</t>
+  </si>
+  <si>
+    <t>0.0492,0.1024,0.8313,0.0741</t>
+  </si>
+  <si>
+    <t>0.1464,0.0265,0.6175,0.2591</t>
+  </si>
+  <si>
+    <t>0.0846,0.0364,0.6796,0.2621</t>
+  </si>
+  <si>
+    <t>0.0396,0.0683,0.8196,0.1313</t>
+  </si>
+  <si>
+    <t>0.7816,0.0181,0.0174,0.2404</t>
+  </si>
+  <si>
+    <t>0.0061,0.1078,0.0031,0.9911</t>
+  </si>
+  <si>
+    <t>0.2011,0.0255,0.0167,0.8717</t>
+  </si>
+  <si>
+    <t>0.1301,0.0227,0.0060,0.9325</t>
+  </si>
+  <si>
+    <t>0.0155,0.0134,0.0021,0.9915</t>
+  </si>
+  <si>
+    <t>0.3330,0.3566,0.0652,0.5457</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2124,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2180,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2264,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3888,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4126,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4770,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4812,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5176,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5190,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5204,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5512,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
